--- a/data/trans_orig/RUIDO_1-Clase-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del ruido en 2023</t>
+          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del ruido en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>9643</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12258</t>
+          <t>10701</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10391</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>786</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12875</t>
+          <t>13986</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6328</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>6661</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10643</t>
+          <t>10973</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7626</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14321</t>
+          <t>15525</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9681</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8023</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10386</t>
+          <t>10977</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17425</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23534</t>
+          <t>22630</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>10068</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25921</t>
+          <t>26310</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9793</t>
+          <t>9577</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22038</t>
+          <t>21641</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22564</t>
+          <t>22611</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41835</t>
+          <t>42896</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28592</t>
+          <t>28309</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49136</t>
+          <t>49255</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20390</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34751</t>
+          <t>35044</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52799</t>
+          <t>52767</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78703</t>
+          <t>79646</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>168184</t>
+          <t>167596</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>197818</t>
+          <t>197423</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>135711</t>
+          <t>135032</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>158452</t>
+          <t>157141</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>312229</t>
+          <t>310514</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>349632</t>
+          <t>348699</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>72,76%</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>474</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7861</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1434</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>9450</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1644</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10100</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11949</t>
+          <t>12950</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>3572</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2577,12 +2577,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6727</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11966</t>
+          <t>12864</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>975</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8509</t>
+          <t>8596</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>8282</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13786</t>
+          <t>13339</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>9789</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7371</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>13582</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -2881,12 +2881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16820</t>
+          <t>16733</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>18215</t>
+          <t>17051</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21693</t>
+          <t>22049</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13058</t>
+          <t>13314</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12956</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30711</t>
+          <t>31468</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29794</t>
+          <t>30897</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53131</t>
+          <t>52351</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8506</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18942</t>
+          <t>19998</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41506</t>
+          <t>41463</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67941</t>
+          <t>67371</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>166861</t>
+          <t>167682</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>196864</t>
+          <t>197614</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>138831</t>
+          <t>138504</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>155991</t>
+          <t>155916</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>313094</t>
+          <t>312708</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>347361</t>
+          <t>348046</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,6%</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>857</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3398</t>
+          <t>3323</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3499</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4314</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -3676,12 +3676,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3691,12 +3691,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3789,12 +3789,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>916</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -4015,12 +4015,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>798</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>824</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>9088</t>
+          <t>9530</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13557</t>
+          <t>13741</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>15384</t>
+          <t>13007</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>543</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>6835</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>20836</t>
+          <t>22119</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>9070</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>25115</t>
+          <t>25037</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19410</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>37266</t>
+          <t>37937</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13991</t>
+          <t>14554</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>26990</t>
+          <t>27192</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>46317</t>
+          <t>47257</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>163673</t>
+          <t>162369</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>187383</t>
+          <t>188391</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>61497</t>
+          <t>60966</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>71935</t>
+          <t>71918</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>227528</t>
+          <t>229629</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>255881</t>
+          <t>256883</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,57%</t>
         </is>
       </c>
     </row>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>763</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>13008</t>
+          <t>11627</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4880,12 +4880,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>975</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -4923,12 +4923,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>723</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>10570</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>507</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>8978</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>14855</t>
+          <t>14500</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>9959</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>777</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>10912</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -5149,12 +5149,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5164,12 +5164,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5262,12 +5262,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>9782</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>531</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>14955</t>
+          <t>14960</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5375,12 +5375,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>861</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>8331</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>12933</t>
+          <t>11917</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -5488,12 +5488,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>11485</t>
+          <t>12400</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5503,12 +5503,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>21296</t>
+          <t>20078</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>26550</t>
+          <t>26199</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -5601,12 +5601,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>26771</t>
+          <t>28069</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>13794</t>
+          <t>13555</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>10763</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>36034</t>
+          <t>35290</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>20581</t>
+          <t>20450</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>59079</t>
+          <t>62779</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5729,12 +5729,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>8259</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>39477</t>
+          <t>38498</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>31073</t>
+          <t>32197</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>85659</t>
+          <t>89649</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -5827,12 +5827,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>33821</t>
+          <t>33416</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>57519</t>
+          <t>57233</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>17272</t>
+          <t>16665</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>74042</t>
+          <t>72582</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>48065</t>
+          <t>46251</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>116570</t>
+          <t>115472</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>390574</t>
+          <t>387371</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>437360</t>
+          <t>436018</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>443383</t>
+          <t>443228</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>559446</t>
+          <t>554077</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>855933</t>
+          <t>855360</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1014908</t>
+          <t>1012674</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,83%</t>
         </is>
       </c>
     </row>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -6283,12 +6283,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>3080</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -6396,12 +6396,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -6509,12 +6509,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6559,12 +6559,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6594,12 +6594,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>808</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>9292</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>7782</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>630</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -6848,12 +6848,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>10698</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>127312</t>
+          <t>128517</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>129319</t>
+          <t>147088</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>809</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>10313</t>
+          <t>9624</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>6763</t>
+          <t>6954</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>2933</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>13526</t>
+          <t>13072</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -7074,12 +7074,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>16958</t>
+          <t>17219</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7089,12 +7089,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>8719</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>21557</t>
+          <t>21172</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7124,12 +7124,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>15146</t>
+          <t>15058</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>33595</t>
+          <t>34525</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -7187,12 +7187,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>12271</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>29524</t>
+          <t>29168</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>18747</t>
+          <t>18579</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>35737</t>
+          <t>35329</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>35032</t>
+          <t>34693</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>59643</t>
+          <t>58684</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -7300,12 +7300,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>177044</t>
+          <t>177133</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>201517</t>
+          <t>201417</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>213819</t>
+          <t>215592</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>328932</t>
+          <t>329638</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>408804</t>
+          <t>398052</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>521009</t>
+          <t>521168</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,53%</t>
         </is>
       </c>
     </row>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7545,12 +7545,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -7643,12 +7643,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>972</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>916</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -7869,12 +7869,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7982,12 +7982,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -7997,12 +7997,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>20255</t>
+          <t>22038</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>24625</t>
+          <t>24967</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>25749</t>
+          <t>27524</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>24828</t>
+          <t>26514</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>39357</t>
+          <t>42153</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -8321,12 +8321,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8356,12 +8356,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>373</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -8434,12 +8434,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>20314</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>5638</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>13772</t>
+          <t>14014</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9437</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>30933</t>
+          <t>30072</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -8547,12 +8547,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>27495</t>
+          <t>29523</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>41018</t>
+          <t>41063</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>69948</t>
+          <t>68458</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>51678</t>
+          <t>52289</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>87223</t>
+          <t>88376</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -8660,12 +8660,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>58038</t>
+          <t>54620</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>90993</t>
+          <t>90853</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>316135</t>
+          <t>314446</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>349402</t>
+          <t>347873</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>384125</t>
+          <t>380688</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>433000</t>
+          <t>431545</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,37%</t>
         </is>
       </c>
     </row>
@@ -8890,12 +8890,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>18016</t>
+          <t>19182</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8925,12 +8925,12 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>13662</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>22745</t>
+          <t>22768</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>16431</t>
+          <t>16460</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>14160</t>
+          <t>13952</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>32304</t>
+          <t>33227</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -9116,12 +9116,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>10580</t>
+          <t>9525</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>12469</t>
+          <t>12261</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -9229,12 +9229,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9244,12 +9244,12 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>7341</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -9342,12 +9342,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>8950</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>25011</t>
+          <t>24131</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9357,12 +9357,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>19274</t>
+          <t>19021</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>19150</t>
+          <t>18401</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>38330</t>
+          <t>38776</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -9455,12 +9455,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>10779</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>42157</t>
+          <t>37977</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9470,12 +9470,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9490,12 +9490,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>17378</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>20443</t>
+          <t>19309</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>51478</t>
+          <t>47597</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>18385</t>
+          <t>19020</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>50665</t>
+          <t>50512</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>33980</t>
+          <t>35395</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>202620</t>
+          <t>196727</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>64304</t>
+          <t>61808</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>260286</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -9681,12 +9681,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>21470</t>
+          <t>21396</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>46234</t>
+          <t>46661</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9716,12 +9716,12 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>25714</t>
+          <t>24538</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9751,12 +9751,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>35202</t>
+          <t>35023</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>66160</t>
+          <t>66246</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>70045</t>
+          <t>69438</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>125556</t>
+          <t>116747</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -9809,12 +9809,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>48008</t>
+          <t>48763</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>88302</t>
+          <t>88387</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>132636</t>
+          <t>130079</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>198333</t>
+          <t>195307</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -9907,12 +9907,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>158052</t>
+          <t>157223</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>209841</t>
+          <t>209703</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -9922,12 +9922,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>121907</t>
+          <t>124233</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>204772</t>
+          <t>204824</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>298688</t>
+          <t>289027</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>402052</t>
+          <t>397057</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>1183338</t>
+          <t>1183793</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>1259146</t>
+          <t>1262388</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10035,12 +10035,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>1419959</t>
+          <t>1415164</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1614582</t>
+          <t>1599798</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>2628903</t>
+          <t>2637306</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>2848305</t>
+          <t>2856040</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_1-Clase-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Clase-trans_orig.xlsx
@@ -725,22 +725,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>10719</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5542</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>2499</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>12892</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4192</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10391</t>
+          <t>15721</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>10026</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13986</t>
+          <t>19103</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6661</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -1177,27 +1177,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10973</t>
+          <t>11805</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>972</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7863</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15525</t>
+          <t>15523</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10088</t>
+          <t>10263</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>3581</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>7650</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>14145</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -1403,32 +1403,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4668</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10977</t>
+          <t>11749</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,32 +1438,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9014</t>
+          <t>9517</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>16965</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13682</t>
+          <t>14878</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8100</t>
+          <t>9061</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22630</t>
+          <t>23572</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -1516,102 +1516,102 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>10646</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3903</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1471</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>8908</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>8799</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>5061</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>15987</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>1,69%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>3889</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>8114</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>8363</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>4404</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>14856</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -1629,32 +1629,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>18295</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>11146</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26310</t>
+          <t>28251</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1664,32 +1664,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14755</t>
+          <t>19367</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9577</t>
+          <t>13498</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21641</t>
+          <t>30446</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>31408</t>
+          <t>37662</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22611</t>
+          <t>26451</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42896</t>
+          <t>48918</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37872</t>
+          <t>40346</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28309</t>
+          <t>30616</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49255</t>
+          <t>53362</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1777,32 +1777,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26785</t>
+          <t>28637</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20203</t>
+          <t>21360</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35044</t>
+          <t>37933</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>64657</t>
+          <t>68983</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52767</t>
+          <t>55993</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79646</t>
+          <t>83957</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -1855,32 +1855,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>183376</t>
+          <t>195092</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>167596</t>
+          <t>177475</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>197423</t>
+          <t>209211</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1890,32 +1890,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>147470</t>
+          <t>160109</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>135032</t>
+          <t>146601</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157141</t>
+          <t>171763</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>330845</t>
+          <t>355201</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>310514</t>
+          <t>333815</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348699</t>
+          <t>374260</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>71,89%</t>
         </is>
       </c>
     </row>
@@ -1968,17 +1968,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>264783</t>
+          <t>285282</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>264783</t>
+          <t>285282</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>264783</t>
+          <t>285282</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>214433</t>
+          <t>235308</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>214433</t>
+          <t>235308</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>214433</t>
+          <t>235308</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2038,17 +2038,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>479216</t>
+          <t>520590</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>479216</t>
+          <t>520590</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>479216</t>
+          <t>520590</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1577</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2095,12 +2095,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>497</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9450</t>
+          <t>10047</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9653</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>809</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4613</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>809</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>4466</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>11859</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2572,32 +2572,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6858</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2607,32 +2607,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>5645</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12864</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -2650,32 +2650,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>838</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2685,32 +2685,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>727</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8282</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2720,32 +2720,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13339</t>
+          <t>11809</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -2763,32 +2763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9789</t>
+          <t>11040</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2798,32 +2798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,32 +2833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>7696</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13582</t>
+          <t>14839</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -2876,32 +2876,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16733</t>
+          <t>18354</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>469</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>9582</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17051</t>
+          <t>20606</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -2989,32 +2989,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>13596</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22049</t>
+          <t>25290</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3024,32 +3024,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13314</t>
+          <t>16076</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>19979</t>
+          <t>23538</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>15902</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31468</t>
+          <t>34818</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -3102,32 +3102,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>40290</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>31986</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>52351</t>
+          <t>56452</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3137,32 +3137,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>12918</t>
+          <t>14246</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8448</t>
+          <t>9093</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19998</t>
+          <t>20664</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>53208</t>
+          <t>57367</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41463</t>
+          <t>43774</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67371</t>
+          <t>71374</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -3215,32 +3215,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>182831</t>
+          <t>190128</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>167682</t>
+          <t>173050</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>197614</t>
+          <t>204407</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3250,32 +3250,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>148150</t>
+          <t>161721</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>138504</t>
+          <t>151129</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>155916</t>
+          <t>170164</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3285,32 +3285,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>330981</t>
+          <t>351849</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>312708</t>
+          <t>332725</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>348046</t>
+          <t>369530</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>77,91%</t>
         </is>
       </c>
     </row>
@@ -3328,17 +3328,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>258607</t>
+          <t>272098</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>258607</t>
+          <t>272098</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>258607</t>
+          <t>272098</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>184186</t>
+          <t>202193</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>184186</t>
+          <t>202193</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>184186</t>
+          <t>202193</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,17 +3398,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>442793</t>
+          <t>474291</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>442793</t>
+          <t>474291</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>442793</t>
+          <t>474291</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>694</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>797</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>797</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>886</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>847</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -4010,32 +4010,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4080,22 +4080,22 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>926</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>9530</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4133,12 +4133,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>14678</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>772</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>679</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>13007</t>
+          <t>16194</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4246,12 +4246,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>525</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -4281,12 +4281,12 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4306,32 +4306,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>2477</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>539</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -4349,32 +4349,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>12178</t>
+          <t>14198</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>7554</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>22119</t>
+          <t>24029</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4384,32 +4384,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>703</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>7229</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,32 +4419,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>15264</t>
+          <t>17492</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>9070</t>
+          <t>10245</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>25037</t>
+          <t>28968</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -4462,32 +4462,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>26798</t>
+          <t>27571</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19181</t>
+          <t>19614</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>37937</t>
+          <t>38322</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4497,32 +4497,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>9189</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>14554</t>
+          <t>16005</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4532,32 +4532,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>35987</t>
+          <t>37854</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>27192</t>
+          <t>28961</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>47257</t>
+          <t>49500</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -4575,32 +4575,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>176687</t>
+          <t>198132</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>162369</t>
+          <t>181309</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>188391</t>
+          <t>209851</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4610,32 +4610,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>67116</t>
+          <t>76433</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>60966</t>
+          <t>69709</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>71918</t>
+          <t>81448</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4645,32 +4645,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>243802</t>
+          <t>274565</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>229629</t>
+          <t>257867</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>256883</t>
+          <t>287313</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,51%</t>
         </is>
       </c>
     </row>
@@ -4688,17 +4688,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>225849</t>
+          <t>251213</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>225849</t>
+          <t>251213</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>225849</t>
+          <t>251213</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4723,17 +4723,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>81543</t>
+          <t>92847</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>81543</t>
+          <t>92847</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>81543</t>
+          <t>92847</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4758,17 +4758,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>307392</t>
+          <t>344060</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>307392</t>
+          <t>344060</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>307392</t>
+          <t>344060</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4805,102 +4805,102 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>851</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>11627</t>
+          <t>12304</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3552</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>4935</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>14150</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
           <t>0,14%</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>3590</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>4693</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>13870</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -4918,22 +4918,22 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>807</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>10570</t>
+          <t>10250</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4953,32 +4953,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>767</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>8978</t>
+          <t>7968</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4988,32 +4988,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>6964</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2333</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>14500</t>
+          <t>15206</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6219</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2373</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5101,17 +5101,17 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>696</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>10912</t>
+          <t>8434</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -5257,32 +5257,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>10200</t>
+          <t>11135</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5292,32 +5292,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>7616</t>
+          <t>8274</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5327,32 +5327,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>7214</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>14188</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -5370,67 +5370,67 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>875</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>8331</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>2273</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>6662</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>2228</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>7049</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5440,32 +5440,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>11917</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -5483,32 +5483,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>12400</t>
+          <t>11544</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5518,32 +5518,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>10032</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>20078</t>
+          <t>17955</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>15543</t>
+          <t>15751</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>26199</t>
+          <t>25167</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -5596,32 +5596,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>15101</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>8555</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>28069</t>
+          <t>27486</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5631,32 +5631,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>13555</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,32 +5666,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>21961</t>
+          <t>22889</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>11577</t>
+          <t>14809</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>35290</t>
+          <t>36044</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5709,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>34893</t>
+          <t>31833</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>20450</t>
+          <t>18741</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>62779</t>
+          <t>49301</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5744,32 +5744,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>22566</t>
+          <t>24906</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>7457</t>
+          <t>16859</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>38498</t>
+          <t>34027</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5779,32 +5779,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>57460</t>
+          <t>56739</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>32197</t>
+          <t>41294</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>89649</t>
+          <t>79808</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -5822,32 +5822,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>44557</t>
+          <t>50141</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>33416</t>
+          <t>38907</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>57233</t>
+          <t>66320</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5857,32 +5857,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>44645</t>
+          <t>46984</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>16665</t>
+          <t>37185</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>72582</t>
+          <t>57863</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5892,32 +5892,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>89202</t>
+          <t>97125</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>46251</t>
+          <t>79803</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>115472</t>
+          <t>114547</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -5935,32 +5935,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>415595</t>
+          <t>449628</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>387371</t>
+          <t>425089</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>436018</t>
+          <t>470376</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5970,32 +5970,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>500042</t>
+          <t>326314</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>443228</t>
+          <t>310460</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>554077</t>
+          <t>340418</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6005,32 +6005,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>915638</t>
+          <t>775941</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>855360</t>
+          <t>744150</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1012674</t>
+          <t>800243</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>80,31%</t>
         </is>
       </c>
     </row>
@@ -6048,17 +6048,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>531331</t>
+          <t>568987</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>531331</t>
+          <t>568987</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>531331</t>
+          <t>568987</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6083,17 +6083,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>595995</t>
+          <t>427498</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>595995</t>
+          <t>427498</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>595995</t>
+          <t>427498</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6118,17 +6118,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>1127327</t>
+          <t>996485</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1127327</t>
+          <t>996485</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1127327</t>
+          <t>996485</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -6210,12 +6210,12 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>705</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>705</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>707</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>707</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>3460</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6652,32 +6652,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6687,27 +6687,27 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>4637</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>9292</t>
+          <t>10193</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>9298</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1423</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>4367</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -6843,32 +6843,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>7255</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>10698</t>
+          <t>15267</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6878,32 +6878,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>37606</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>128517</t>
+          <t>10245</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6913,32 +6913,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>42967</t>
+          <t>12622</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>6831</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>147088</t>
+          <t>21048</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -6956,67 +6956,67 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>881</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>9624</t>
+          <t>8178</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>3720</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>8170</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>3186</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>1216</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>6954</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O59" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7026,32 +7026,32 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>13072</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -7069,32 +7069,32 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>3487</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>17219</t>
+          <t>23202</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7104,32 +7104,32 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>14336</t>
+          <t>15479</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>9815</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>21172</t>
+          <t>22573</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7139,32 +7139,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>22729</t>
+          <t>27206</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>15058</t>
+          <t>18128</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>34525</t>
+          <t>39223</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -7182,32 +7182,32 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>19581</t>
+          <t>21563</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>12819</t>
+          <t>13371</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>31776</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7217,32 +7217,32 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>26415</t>
+          <t>30989</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>18579</t>
+          <t>23559</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>35329</t>
+          <t>41007</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7252,32 +7252,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>45996</t>
+          <t>52552</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>34693</t>
+          <t>40853</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>58684</t>
+          <t>64922</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -7295,32 +7295,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>189996</t>
+          <t>225531</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>177133</t>
+          <t>210694</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>201417</t>
+          <t>236498</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7330,32 +7330,32 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>298258</t>
+          <t>337414</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>215592</t>
+          <t>323635</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>329638</t>
+          <t>348135</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7365,32 +7365,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>488254</t>
+          <t>562945</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>398052</t>
+          <t>544304</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>521168</t>
+          <t>579900</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>86,12%</t>
         </is>
       </c>
     </row>
@@ -7408,17 +7408,17 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>230111</t>
+          <t>272590</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>230111</t>
+          <t>272590</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>230111</t>
+          <t>272590</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>386464</t>
+          <t>400794</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>386464</t>
+          <t>400794</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>386464</t>
+          <t>400794</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7478,17 +7478,17 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>616575</t>
+          <t>673384</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>616575</t>
+          <t>673384</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>616575</t>
+          <t>673384</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7510,7 +7510,7 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>615</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>615</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -7683,12 +7683,12 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -7761,12 +7761,12 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -8012,7 +8012,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>401</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -8022,12 +8022,12 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>401</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="V68" s="2" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>22038</t>
+          <t>24952</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>24967</t>
+          <t>25697</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>7994</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>27524</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>13828</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>26514</t>
+          <t>26654</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8273,32 +8273,32 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>20588</t>
+          <t>21822</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10212</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>42153</t>
+          <t>41442</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -8351,32 +8351,32 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>350</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8386,32 +8386,32 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>344</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -8429,32 +8429,32 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>20740</t>
+          <t>17633</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8464,32 +8464,32 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>14014</t>
+          <t>15133</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8499,32 +8499,32 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>16235</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>10036</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>30072</t>
+          <t>29644</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -8542,32 +8542,32 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>12969</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>6341</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>29523</t>
+          <t>24777</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8577,32 +8577,32 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>53830</t>
+          <t>57374</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>41063</t>
+          <t>45514</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>68458</t>
+          <t>72461</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8612,32 +8612,32 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>67672</t>
+          <t>70343</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>52289</t>
+          <t>54477</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>88376</t>
+          <t>87905</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -8655,32 +8655,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>76179</t>
+          <t>79205</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>54620</t>
+          <t>61190</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>90853</t>
+          <t>93283</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8690,32 +8690,32 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>334015</t>
+          <t>370785</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>314446</t>
+          <t>353531</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>347873</t>
+          <t>385990</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8725,32 +8725,32 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>410193</t>
+          <t>449989</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>380688</t>
+          <t>424151</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>431545</t>
+          <t>470954</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,79%</t>
         </is>
       </c>
     </row>
@@ -8768,17 +8768,17 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>110639</t>
+          <t>112977</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>110639</t>
+          <t>112977</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>110639</t>
+          <t>112977</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8803,17 +8803,17 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>413291</t>
+          <t>455906</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>413291</t>
+          <t>455906</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>413291</t>
+          <t>455906</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -8838,17 +8838,17 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>523929</t>
+          <t>568882</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>523929</t>
+          <t>568882</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>523929</t>
+          <t>568882</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8885,32 +8885,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>11575</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>20023</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8920,32 +8920,32 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>13662</t>
+          <t>14881</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8955,32 +8955,32 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>16426</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>12173</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>26844</t>
+          <t>31152</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -8998,102 +8998,102 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>15512</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>8142</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>22768</t>
+          <t>27386</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>10341</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>6284</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>17151</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>25853</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>17228</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="inlineStr">
+        <is>
+          <t>38859</t>
+        </is>
+      </c>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>9284</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>4666</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>16460</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="O77" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="P77" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="Q77" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R77" s="2" t="inlineStr">
-        <is>
-          <t>22245</t>
-        </is>
-      </c>
-      <c r="S77" s="2" t="inlineStr">
-        <is>
-          <t>13952</t>
-        </is>
-      </c>
-      <c r="T77" s="2" t="inlineStr">
-        <is>
-          <t>33227</t>
-        </is>
-      </c>
-      <c r="U77" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="V77" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -9111,32 +9111,32 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>11382</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9146,32 +9146,32 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>9525</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9181,32 +9181,32 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>14321</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -9259,22 +9259,22 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>713</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>7039</t>
+          <t>6692</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9294,17 +9294,17 @@
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>7765</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
     </row>
@@ -9337,32 +9337,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>15378</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>24131</t>
+          <t>24958</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9372,32 +9372,32 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>14605</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>8831</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>19021</t>
+          <t>21523</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9407,32 +9407,32 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>27196</t>
+          <t>29983</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>18401</t>
+          <t>21373</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>38776</t>
+          <t>41541</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -9450,32 +9450,32 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>20097</t>
+          <t>19203</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>10779</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>37977</t>
+          <t>35453</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9485,67 +9485,67 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10439</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>17505</t>
+          <t>16712</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>29642</t>
+        </is>
+      </c>
+      <c r="S81" s="2" t="inlineStr">
+        <is>
+          <t>19271</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="inlineStr">
+        <is>
+          <t>46376</t>
+        </is>
+      </c>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
           <t>0,54%</t>
         </is>
       </c>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="P81" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="Q81" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R81" s="2" t="inlineStr">
-        <is>
-          <t>30308</t>
-        </is>
-      </c>
-      <c r="S81" s="2" t="inlineStr">
-        <is>
-          <t>19309</t>
-        </is>
-      </c>
-      <c r="T81" s="2" t="inlineStr">
-        <is>
-          <t>47597</t>
-        </is>
-      </c>
-      <c r="U81" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="V81" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -9563,32 +9563,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>30922</t>
+          <t>34281</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>19020</t>
+          <t>23537</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>50512</t>
+          <t>55175</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9598,32 +9598,32 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>73432</t>
+          <t>43401</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>35395</t>
+          <t>32209</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>196727</t>
+          <t>60277</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9633,32 +9633,32 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>104354</t>
+          <t>77681</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>61808</t>
+          <t>60136</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>260286</t>
+          <t>100387</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -9676,32 +9676,32 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>32247</t>
+          <t>33414</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>21396</t>
+          <t>22542</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>46661</t>
+          <t>49501</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9711,32 +9711,32 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>18881</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>9636</t>
+          <t>13478</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>24538</t>
+          <t>27432</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9746,32 +9746,32 @@
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>49252</t>
+          <t>52296</t>
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>35023</t>
+          <t>38275</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>66246</t>
+          <t>69814</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -9789,32 +9789,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>91272</t>
+          <t>96408</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>69438</t>
+          <t>76244</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>116747</t>
+          <t>122511</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9824,32 +9824,32 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>71803</t>
+          <t>82768</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>48763</t>
+          <t>70195</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>88387</t>
+          <t>98198</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9859,32 +9859,32 @@
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>163075</t>
+          <t>179176</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>130079</t>
+          <t>154721</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>195307</t>
+          <t>210488</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -9902,32 +9902,32 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>182940</t>
+          <t>195711</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>157223</t>
+          <t>170581</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>209703</t>
+          <t>224434</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9937,32 +9937,32 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>173782</t>
+          <t>188512</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>124233</t>
+          <t>165896</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>204824</t>
+          <t>210084</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9972,32 +9972,32 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>356722</t>
+          <t>384223</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>289027</t>
+          <t>347336</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>397057</t>
+          <t>420337</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -10015,32 +10015,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>1224663</t>
+          <t>1337716</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>1183793</t>
+          <t>1292722</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>1262388</t>
+          <t>1372319</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10050,32 +10050,32 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>1495050</t>
+          <t>1432775</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>1415164</t>
+          <t>1402155</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1599798</t>
+          <t>1461856</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10085,32 +10085,32 @@
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>2719714</t>
+          <t>2770490</t>
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>2637306</t>
+          <t>2722696</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>2856040</t>
+          <t>2820565</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>78,84%</t>
         </is>
       </c>
     </row>
@@ -10128,17 +10128,17 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>1621320</t>
+          <t>1763147</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>1621320</t>
+          <t>1763147</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>1621320</t>
+          <t>1763147</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -10163,17 +10163,17 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>1875912</t>
+          <t>1814545</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>1875912</t>
+          <t>1814545</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>1875912</t>
+          <t>1814545</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10198,17 +10198,17 @@
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>3497233</t>
+          <t>3577691</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>3497233</t>
+          <t>3577691</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>3497233</t>
+          <t>3577691</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">

--- a/data/trans_orig/RUIDO_1-Clase-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del ruido en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del ruido en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
